--- a/docs/assets/infraestructura/s2-e1-inventario-activos.xlsx
+++ b/docs/assets/infraestructura/s2-e1-inventario-activos.xlsx
@@ -592,7 +592,7 @@
     <col min="10" max="10" width="8.83203125" customWidth="1"/>
     <col min="11" max="11" width="15.83203125" customWidth="1"/>
     <col min="12" max="12" width="12.83203125" customWidth="1"/>
-    <col min="13" max="13" width="44.83203125" customWidth="1"/>
+    <col min="13" max="13" width="37.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -879,7 +879,7 @@
         <v>Alta</v>
       </c>
       <c r="M7" t="str">
-        <v>Operativo (versión corregida sin publicar)</v>
+        <v>Operativo (publicada 2026-10-24)</v>
       </c>
     </row>
     <row r="8">
@@ -961,7 +961,7 @@
         <v>Alta</v>
       </c>
       <c r="M9" t="str">
-        <v>Operativo (con hallazgo NC-03)</v>
+        <v>Operativo (clave rotada 2026-10-24)</v>
       </c>
     </row>
     <row r="10">

--- a/docs/assets/infraestructura/s2-e1-inventario-activos.xlsx
+++ b/docs/assets/infraestructura/s2-e1-inventario-activos.xlsx
@@ -585,7 +585,7 @@
     <col min="3" max="3" width="26.83203125" customWidth="1"/>
     <col min="4" max="4" width="26.83203125" customWidth="1"/>
     <col min="5" max="5" width="29.83203125" customWidth="1"/>
-    <col min="6" max="6" width="38.83203125" customWidth="1"/>
+    <col min="6" max="6" width="60.83203125" customWidth="1"/>
     <col min="7" max="7" width="19.83203125" customWidth="1"/>
     <col min="8" max="8" width="8.83203125" customWidth="1"/>
     <col min="9" max="9" width="8.83203125" customWidth="1"/>
@@ -981,7 +981,7 @@
         <v>Encargado de TI</v>
       </c>
       <c r="F10" t="str">
-        <v>PC local, VPS, PBS y disco externo</v>
+        <v>VPS (respaldo diario de MySQL), PC (copia semanal), PBS y disco externo</v>
       </c>
       <c r="G10" t="str">
         <v>Restringida</v>
@@ -1063,7 +1063,7 @@
         <v>Encargado de TI</v>
       </c>
       <c r="F12" t="str">
-        <v>VPS, PC local y VM-SIEM01</v>
+        <v>VPS y VM-SIEM01</v>
       </c>
       <c r="G12" t="str">
         <v>Confidencial</v>
@@ -1268,7 +1268,7 @@
         <v>Equipo técnico</v>
       </c>
       <c r="F17" t="str">
-        <v>PC local (destino: VM-APP01)</v>
+        <v>VPS del colegio, usuario academia (destino de diseño: VM-APP01)</v>
       </c>
       <c r="G17" t="str">
         <v>Interna</v>
@@ -1289,7 +1289,7 @@
         <v>Alta</v>
       </c>
       <c r="M17" t="str">
-        <v>Transitorio</v>
+        <v>Operativo (VPS desde 2026-10-24)</v>
       </c>
     </row>
     <row r="18">
@@ -1309,7 +1309,7 @@
         <v>Equipo técnico</v>
       </c>
       <c r="F18" t="str">
-        <v>PC local (destino: VM-APP01)</v>
+        <v>VPS del colegio (destino de diseño: VM-APP01)</v>
       </c>
       <c r="G18" t="str">
         <v>Restringida</v>
@@ -1330,7 +1330,7 @@
         <v>Alta</v>
       </c>
       <c r="M18" t="str">
-        <v>Transitorio</v>
+        <v>Operativo (VPS desde 2026-10-24)</v>
       </c>
     </row>
     <row r="19">
@@ -1420,7 +1420,7 @@
         <v>ACT-20</v>
       </c>
       <c r="B21" t="str">
-        <v>PC local con PM2 (servicios transitorios)</v>
+        <v>PC local con PM2 (servicios anteriores de la capa)</v>
       </c>
       <c r="C21" t="str">
         <v>Infraestructura</v>
@@ -1453,7 +1453,7 @@
         <v>Alta</v>
       </c>
       <c r="M21" t="str">
-        <v>Transitorio</v>
+        <v>Retirado (2026-10-24)</v>
       </c>
     </row>
     <row r="22">
